--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484757_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484757_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.924</v>
+        <v>3.5117</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4856</v>
+        <v>2.9727</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4384</v>
+        <v>0.539</v>
       </c>
       <c r="G2" t="n">
         <v>0.9514</v>
@@ -610,13 +610,13 @@
         <v>1.6983</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.1457</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.585</v>
+        <v>-0.0978</v>
       </c>
       <c r="U2" t="n">
-        <v>1.143</v>
+        <v>0.2435</v>
       </c>
       <c r="V2" t="n">
         <v>4.679</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7796</v>
+        <v>3.0447</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2373</v>
+        <v>3.5552</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4576</v>
+        <v>-0.5105</v>
       </c>
       <c r="G3" t="n">
         <v>5.4809</v>
@@ -688,13 +688,13 @@
         <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5403</v>
+        <v>-0.1947</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8905</v>
+        <v>0.2085</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3502</v>
+        <v>-0.4031</v>
       </c>
       <c r="V3" t="n">
         <v>-1.1093</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2896</v>
+        <v>2.7587</v>
       </c>
       <c r="E4" t="n">
-        <v>2.6874</v>
+        <v>3.0771</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3978</v>
+        <v>-0.3184</v>
       </c>
       <c r="G4" t="n">
         <v>3.27</v>
@@ -766,13 +766,13 @@
         <v>1.3209</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3615</v>
+        <v>0.1076</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.291</v>
+        <v>0.0987</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.0089</v>
       </c>
       <c r="V4" t="n">
         <v>0.1359</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1156</v>
+        <v>-0.249</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3561</v>
+        <v>0.674</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2405</v>
+        <v>-0.923</v>
       </c>
       <c r="G6" t="n">
         <v>1.2114</v>
@@ -922,13 +922,13 @@
         <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3909</v>
+        <v>0.0263</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1844</v>
+        <v>0.5024</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7935</v>
+        <v>-0.4761</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1093</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3429</v>
+        <v>-1.3164</v>
       </c>
       <c r="E7" t="n">
         <v>-0.9812</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3617</v>
+        <v>-0.3353</v>
       </c>
       <c r="G7" t="n">
         <v>0.0697</v>
@@ -1000,13 +1000,13 @@
         <v>0.1887</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1711</v>
+        <v>-0.1446</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0588</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V7" t="n">
         <v>-0.4867</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1714</v>
+        <v>-3.5881</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.982</v>
+        <v>-1.6897</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1894</v>
+        <v>-1.8984</v>
       </c>
       <c r="G8" t="n">
         <v>-1.7281</v>
@@ -1078,13 +1078,13 @@
         <v>1.3209</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.3867</v>
+        <v>-0.8034</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4115</v>
+        <v>-0.1192</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9752</v>
+        <v>-0.6842</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.8995</v>
+        <v>-4.5543</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.6064</v>
+        <v>-6.3141</v>
       </c>
       <c r="F9" t="n">
-        <v>1.707</v>
+        <v>1.7599</v>
       </c>
       <c r="G9" t="n">
         <v>-4.5583</v>
@@ -1156,13 +1156,13 @@
         <v>1.3209</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5678</v>
+        <v>-0.2226</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9994</v>
+        <v>-0.7071</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4316</v>
+        <v>0.4845</v>
       </c>
       <c r="V9" t="n">
         <v>0.038</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5879</v>
+        <v>-5.5001</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0979</v>
+        <v>-4.1953</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.49</v>
+        <v>-1.3048</v>
       </c>
       <c r="G10" t="n">
         <v>0.0562</v>
@@ -1234,13 +1234,13 @@
         <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6096</v>
+        <v>-0.5218</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2997</v>
+        <v>0.2023</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9093</v>
+        <v>-0.7241</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5057</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.959000000000001</v>
+        <v>-4.958899999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.967199999999999</v>
+        <v>-1.967399999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9916</v>
+        <v>-2.9915</v>
       </c>
       <c r="G11" t="n">
         <v>5.687099999999998</v>
@@ -1315,7 +1315,7 @@
         <v>-1.6075</v>
       </c>
       <c r="T11" t="n">
-        <v>0.02890000000000015</v>
+        <v>0.029</v>
       </c>
       <c r="U11" t="n">
         <v>-1.6364</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.054</v>
+        <v>6.4602</v>
       </c>
       <c r="E12" t="n">
-        <v>5.8777</v>
+        <v>4.4162</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1763</v>
+        <v>2.044</v>
       </c>
       <c r="G12" t="n">
         <v>-0.108</v>
@@ -1390,13 +1390,13 @@
         <v>3.3966</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4636</v>
+        <v>0.8698</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2513</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2123</v>
+        <v>0.08</v>
       </c>
       <c r="V12" t="n">
         <v>2.4904</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.4394</v>
+        <v>4.5638</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7461</v>
+        <v>4.1615</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6933</v>
+        <v>0.4023</v>
       </c>
       <c r="G13" t="n">
         <v>1.9315</v>
@@ -1468,13 +1468,13 @@
         <v>3.0192</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4702</v>
+        <v>0.5946</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0698</v>
+        <v>0.4852</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4004</v>
+        <v>0.1094</v>
       </c>
       <c r="V13" t="n">
         <v>0.9054</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8335</v>
+        <v>1.2151</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1647</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.3312</v>
+        <v>0.3104</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9606</v>
+        <v>2.4185</v>
       </c>
       <c r="H14" t="n">
-        <v>1.926</v>
+        <v>-0.0031</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0346</v>
+        <v>2.4216</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9544</v>
+        <v>4.1924</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4395</v>
+        <v>1.0565</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.485</v>
+        <v>3.1359</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9939</v>
+        <v>-1.7738</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5135</v>
+        <v>-1.0596</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5196</v>
+        <v>-0.7143</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.0757</v>
+        <v>-2.8305</v>
       </c>
       <c r="R14" t="n">
-        <v>1.887</v>
+        <v>3.3966</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8728</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3049</v>
+        <v>-0.4382</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5679</v>
+        <v>-0.3879</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.8112</v>
+        <v>-0.9434</v>
       </c>
       <c r="W14" t="n">
         <v>-0.019</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.7922</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4219</v>
+        <v>-0.2731</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3619</v>
+        <v>1.1903</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0599</v>
+        <v>-1.4634</v>
       </c>
       <c r="G15" t="n">
-        <v>2.4185</v>
+        <v>1.9606</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0031</v>
+        <v>1.926</v>
       </c>
       <c r="I15" t="n">
-        <v>2.4216</v>
+        <v>0.0346</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1924</v>
+        <v>2.9544</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0565</v>
+        <v>3.4395</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1359</v>
+        <v>-0.485</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7738</v>
+        <v>-0.9939</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0596</v>
+        <v>-1.5135</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.7143</v>
+        <v>0.5196</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5661</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8305</v>
+        <v>-2.0757</v>
       </c>
       <c r="R15" t="n">
-        <v>3.3966</v>
+        <v>1.887</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.4631</v>
+        <v>0.7662</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.7048</v>
+        <v>0.3306</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7583</v>
+        <v>0.4356</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9434</v>
+        <v>-2.8112</v>
       </c>
       <c r="W15" t="n">
         <v>-0.019</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.9244</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4911</v>
+        <v>-0.2963</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1306</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F16" t="n">
         <v>-0.3605</v>
@@ -1702,10 +1702,10 @@
         <v>0.5661</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3651</v>
+        <v>-0.1702</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2352</v>
+        <v>-0.0403</v>
       </c>
       <c r="U16" t="n">
         <v>-0.1299</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>M. ISIDRO PENA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3494</v>
+        <v>-0.8872</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.8717</v>
+        <v>0.6598000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5223</v>
+        <v>-1.547</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.3681</v>
+        <v>0.1252</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.4652</v>
+        <v>-1.0956</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9029</v>
+        <v>1.2209</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.7224</v>
+        <v>0.6351</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.1224</v>
+        <v>-0.6073</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5999</v>
+        <v>1.2424</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6457000000000001</v>
+        <v>-0.5099</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3428</v>
+        <v>-0.4883</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.303</v>
+        <v>-0.0216</v>
       </c>
       <c r="P17" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="R17" t="n">
         <v>0.3774</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.0757</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.4531</v>
-      </c>
       <c r="S17" t="n">
-        <v>0.1322</v>
+        <v>0.0441</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4173</v>
+        <v>0.2134</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2851</v>
+        <v>-0.1693</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5091</v>
+        <v>-1.2452</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5091</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ISIDRO PENA</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4092</v>
+        <v>-1.341</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2701</v>
+        <v>-2.9691</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6792</v>
+        <v>1.6281</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1252</v>
+        <v>-3.3681</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0956</v>
+        <v>-2.4652</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2209</v>
+        <v>-0.9029</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6351</v>
+        <v>-2.7224</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6073</v>
+        <v>-2.1224</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2424</v>
+        <v>-0.5999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5099</v>
+        <v>-0.6457000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4883</v>
+        <v>-0.3428</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0216</v>
+        <v>-0.303</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3774</v>
+        <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4779</v>
+        <v>0.1406</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1764</v>
+        <v>0.3199</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3016</v>
+        <v>-0.1793</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2452</v>
+        <v>1.5091</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5091</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8473</v>
+        <v>-2.1141</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9619</v>
+        <v>-3.0587</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1146</v>
+        <v>0.9446</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.6682</v>
+        <v>-3.2864</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2586</v>
+        <v>-2.3705</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.4096</v>
+        <v>-0.9159</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.1714</v>
+        <v>-2.9765</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3461</v>
+        <v>-1.8008</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.8253</v>
+        <v>-1.1757</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4968</v>
+        <v>-0.3099</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9125</v>
+        <v>-0.5697</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5843</v>
+        <v>0.2598</v>
       </c>
       <c r="P19" t="n">
-        <v>2.4531</v>
+        <v>1.1322</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.6418</v>
+        <v>1.1322</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3304</v>
+        <v>0.0401</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5262</v>
+        <v>-0.0822</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1958</v>
+        <v>0.1223</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9244</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8491</v>
+        <v>-2.3685</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.7407</v>
+        <v>-2.3773</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8917</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.2864</v>
+        <v>-4.6682</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3705</v>
+        <v>-2.2586</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9159</v>
+        <v>-2.4096</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.9765</v>
+        <v>-3.1714</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8008</v>
+        <v>-1.3461</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1757</v>
+        <v>-1.8253</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3099</v>
+        <v>-1.4968</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5697</v>
+        <v>-0.9125</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2598</v>
+        <v>-0.5843</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1322</v>
+        <v>2.4531</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1322</v>
+        <v>2.6418</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6949</v>
+        <v>0.1484</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7642</v>
+        <v>0.0584</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0694</v>
+        <v>0.09</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.9244</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="21">
@@ -2047,25 +2047,25 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.958900000000002</v>
+        <v>4.958900000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>2.991799999999999</v>
+        <v>2.991599999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9674</v>
+        <v>1.9673</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.687099999999999</v>
+        <v>-5.687100000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.412100000000001</v>
+        <v>-3.4121</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.274799999999999</v>
+        <v>-2.2748</v>
       </c>
       <c r="J21" t="n">
-        <v>3.753499999999999</v>
+        <v>3.7535</v>
       </c>
       <c r="K21" t="n">
         <v>4.4058</v>
@@ -2077,7 +2077,7 @@
         <v>-9.4405</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.817900000000001</v>
+        <v>-7.8179</v>
       </c>
       <c r="O21" t="n">
         <v>-1.6227</v>
@@ -2086,19 +2086,19 @@
         <v>9.434999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-9.434999999999999</v>
+        <v>-9.435</v>
       </c>
       <c r="R21" t="n">
         <v>18.87</v>
       </c>
       <c r="S21" t="n">
-        <v>1.6074</v>
+        <v>1.6075</v>
       </c>
       <c r="T21" t="n">
-        <v>1.636500000000001</v>
+        <v>1.6366</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.02910000000000003</v>
+        <v>-0.02910000000000004</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3966999999999996</v>
@@ -2107,7 +2107,7 @@
         <v>7.0365</v>
       </c>
       <c r="X21" t="n">
-        <v>-7.4332</v>
+        <v>-7.433200000000001</v>
       </c>
     </row>
   </sheetData>
